--- a/Operacional/clientes/construmais/outputs/10-2026/Arquivos/14-disparo-whatsapp/14-disparo-whatsapp-lote-21.xlsx
+++ b/Operacional/clientes/construmais/outputs/10-2026/Arquivos/14-disparo-whatsapp/14-disparo-whatsapp-lote-21.xlsx
@@ -474,751 +474,751 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>5583988913969</v>
+        <v>5583987004512</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Thiago</t>
+          <t>Edson</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Thiago da Silva Lisboa</t>
+          <t>Edson do Livramento Martins</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
-        <v>5583991271961</v>
+        <v>5583993628733</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Lucineide</t>
+          <t>Wellington</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Lucineide Maciel da Silva</t>
+          <t>Wellington Faustino Soares</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>5583989036601</v>
+        <v>5583994440110</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Nicolas</t>
+          <t>Mundo</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Nicolas Teixera Gomes</t>
+          <t>Mundo das Tintas</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>5583998378455</v>
+        <v>5583987601356</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Marcos</t>
+          <t>Simone</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Marcos Antonio do Nascimento</t>
+          <t>Simone Lima de Almeida</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>5583987631900</v>
+        <v>5583986331990</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Marilene</t>
+          <t>Lucas</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Marilene Andrade de Lima</t>
+          <t>Lucas Alves de Souza Brito</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>5583993646183</v>
+        <v>5583993926033</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Poli</t>
+          <t>Ismael</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Poli X Recicladora</t>
+          <t>Ismael Gomes da Silva</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>5582998396868</v>
+        <v>5583988820496</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Wallaff</t>
+          <t>Antonio</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Wallaff Beethoven</t>
+          <t>Antonio Luna Lisboa Neto</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>5583988433297</v>
+        <v>5583994024580</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Hamilton</t>
+          <t>Fabiano</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Hamilton Rufino da Silva</t>
+          <t>Fabiano Santiago</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>5583986538696</v>
+        <v>5581999040593</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Vandinaldo</t>
+          <t>Romeu</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Vandinaldo Correia da Silva</t>
+          <t>Romeu Soares Batista Filho</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>5522998830048</v>
+        <v>5583981960258</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Lohany</t>
+          <t>Artenuza</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Lohany Janine Crespo da Silva</t>
+          <t>Artenuza Alves</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>5583988488843</v>
+        <v>5583998302851</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Jeane</t>
+          <t>Maria</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Jeane Januario de Souza Chaves</t>
+          <t>Maria do Ceu Sobrinho</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
-        <v>5583986333307</v>
+        <v>5583988051376</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Patricia</t>
+          <t>Luis</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Patricia Jose dos Santos</t>
+          <t>Luis Carlos da Silva Filho</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
-        <v>5583998719036</v>
+        <v>5583986515736</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Alessandro</t>
+          <t>Luiz</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Alessandro da Silva Ferreira</t>
+          <t>Luiz Soares da Costa</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
-        <v>5583996647239</v>
+        <v>5531986981246</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Aderilton</t>
+          <t>Luciana</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Aderilton Batista</t>
+          <t>Luciana Pires</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
-        <v>5583993715420</v>
+        <v>5583988418324</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Alberto</t>
+          <t>Laurenice</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Alberto Magno Aragao</t>
+          <t>Laurenice Victor Souto</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
-        <v>5583986341904</v>
+        <v>5583998205203</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Jhol</t>
+          <t>Agencia</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Jhol Andersson Teixeira Liberto</t>
+          <t>Agencia Sus</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
-        <v>5581999443097</v>
+        <v>5583996134625</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Alexandre</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Maria de Lourdes da Silva</t>
+          <t>Alexandre Lopes da Silva</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
-        <v>5583986649485</v>
+        <v>5583998034594</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Talisson</t>
+          <t>Nayanne</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Talisson Fernandes da Cruz</t>
+          <t>Nayanne Gouveia Pinto Lins</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
-        <v>5583996687517</v>
+        <v>5583988913969</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Joao</t>
+          <t>Thiago</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Joao Batista Matias da Silva</t>
+          <t>Thiago da Silva Lisboa</t>
         </is>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" s="3">
       <c r="A21" s="4" t="n">
-        <v>5583986992248</v>
+        <v>5583991271961</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Solange</t>
+          <t>Lucineide</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Solange Medeiros da Silva</t>
+          <t>Lucineide Maciel da Silva</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1" s="3">
       <c r="A22" s="4" t="n">
-        <v>5521983394840</v>
+        <v>5583989036601</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Gersiana</t>
+          <t>Nicolas</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Gersiana Alves dos Santos</t>
+          <t>Nicolas Teixera Gomes</t>
         </is>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1" s="3">
       <c r="A23" s="4" t="n">
-        <v>5583996926223</v>
+        <v>5583998378455</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Adriano</t>
+          <t>Marcos</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Adriano de Mello Cavalcante</t>
+          <t>Marcos Antonio do Nascimento</t>
         </is>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1" s="3">
       <c r="A24" s="4" t="n">
-        <v>5583988100266</v>
+        <v>5583987631900</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Jaqueline</t>
+          <t>Marilene</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Jaqueline de Araujo Santos</t>
+          <t>Marilene Andrade de Lima</t>
         </is>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1" s="3">
       <c r="A25" s="4" t="n">
-        <v>5583999601813</v>
+        <v>5583993646183</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Mayara</t>
+          <t>Poli</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Mayara Leal Firmino da Silva</t>
+          <t>Poli X Recicladora</t>
         </is>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1" s="3">
       <c r="A26" s="4" t="n">
-        <v>5583986153195</v>
+        <v>5582998396868</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Artur</t>
+          <t>Wallaff</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Artur Guilherme da Silva Rufo</t>
+          <t>Wallaff Beethoven</t>
         </is>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1" s="3">
       <c r="A27" s="4" t="n">
-        <v>5583999217986</v>
+        <v>5583988433297</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Edificio</t>
+          <t>Hamilton</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Edificio Atlantico Sul Residence</t>
+          <t>Hamilton Rufino da Silva</t>
         </is>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1" s="3">
       <c r="A28" s="4" t="n">
-        <v>5583999818805</v>
+        <v>5583986538696</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Yazbek</t>
+          <t>Vandinaldo</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Yazbek Lighting</t>
+          <t>Vandinaldo Correia da Silva</t>
         </is>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1" s="3">
       <c r="A29" s="4" t="n">
-        <v>5583996615352</v>
+        <v>5522998830048</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Carolina</t>
+          <t>Lohany</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Carolina Alves Bernardo</t>
+          <t>Lohany Janine Crespo da Silva</t>
         </is>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1" s="3">
       <c r="A30" s="4" t="n">
-        <v>5583988785668</v>
+        <v>5583988488843</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Jose</t>
+          <t>Jeane</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Jose Herculano de Aquino</t>
+          <t>Jeane Januario de Souza Chaves</t>
         </is>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1" s="3">
       <c r="A31" s="4" t="n">
-        <v>5583987160191</v>
+        <v>5583986333307</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Alexsandro</t>
+          <t>Patricia</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Alexsandro Gomes</t>
+          <t>Patricia Jose dos Santos</t>
         </is>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1" s="3">
       <c r="A32" s="4" t="n">
-        <v>5583988988435</v>
+        <v>5583998719036</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Emmyle</t>
+          <t>Alessandro</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Emmyle Sobral</t>
+          <t>Alessandro da Silva Ferreira</t>
         </is>
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1" s="3">
       <c r="A33" s="4" t="n">
-        <v>5583999818919</v>
+        <v>5583996647239</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Agnes</t>
+          <t>Aderilton</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Agnes Pauli Pontes de Aquino</t>
+          <t>Aderilton Batista</t>
         </is>
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1" s="3">
       <c r="A34" s="4" t="n">
-        <v>5583986344505</v>
+        <v>5583993715420</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Carlos</t>
+          <t>Alberto</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Carlos Antonio Cordeiro de Sousa</t>
+          <t>Alberto Magno Aragao</t>
         </is>
       </c>
     </row>
     <row r="35" ht="15.75" customHeight="1" s="3">
       <c r="A35" s="4" t="n">
-        <v>5583996891137</v>
+        <v>5583986341904</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Residencial</t>
+          <t>Jhol</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Residencial Florenca</t>
+          <t>Jhol Andersson Teixeira Liberto</t>
         </is>
       </c>
     </row>
     <row r="36" ht="15.75" customHeight="1" s="3">
       <c r="A36" s="4" t="n">
-        <v>5543999709926</v>
+        <v>5581999443097</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Rafael</t>
+          <t>Maria</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Rafael Campos</t>
+          <t>Maria de Lourdes da Silva</t>
         </is>
       </c>
     </row>
     <row r="37" ht="15.75" customHeight="1" s="3">
       <c r="A37" s="4" t="n">
-        <v>5583988044505</v>
+        <v>5583986649485</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Rodolfo</t>
+          <t>Talisson</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Rodolfo Hiroshi</t>
+          <t>Talisson Fernandes da Cruz</t>
         </is>
       </c>
     </row>
     <row r="38" ht="15.75" customHeight="1" s="3">
       <c r="A38" s="4" t="n">
-        <v>5583988220845</v>
+        <v>5583996687517</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Manoel</t>
+          <t>Joao</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Manoel Rodrigues de S Filho</t>
+          <t>Joao Batista Matias da Silva</t>
         </is>
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1" s="3">
       <c r="A39" s="4" t="n">
-        <v>5583993828124</v>
+        <v>5583986992248</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Jose</t>
+          <t>Solange</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Jose Wellington Freitas</t>
+          <t>Solange Medeiros da Silva</t>
         </is>
       </c>
     </row>
     <row r="40" ht="15.75" customHeight="1" s="3">
       <c r="A40" s="4" t="n">
-        <v>5583988033861</v>
+        <v>5521983394840</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Vitoria</t>
+          <t>Gersiana</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Vitoria Jaqueline Fernandes da Fonseca</t>
+          <t>Gersiana Alves dos Santos</t>
         </is>
       </c>
     </row>
     <row r="41" ht="15.75" customHeight="1" s="3">
       <c r="A41" s="4" t="n">
-        <v>5521983043465</v>
+        <v>5583996926223</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Ernades</t>
+          <t>Adriano</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Ernades Datas da Silva</t>
+          <t>Adriano de Mello Cavalcante</t>
         </is>
       </c>
     </row>
     <row r="42" ht="15.75" customHeight="1" s="3">
       <c r="A42" s="4" t="n">
-        <v>5583998245941</v>
+        <v>5583988100266</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Marcelo</t>
+          <t>Jaqueline</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Marcelo da Fonseca Silva</t>
+          <t>Jaqueline de Araujo Santos</t>
         </is>
       </c>
     </row>
     <row r="43" ht="15.75" customHeight="1" s="3">
       <c r="A43" s="4" t="n">
-        <v>5583988816212</v>
+        <v>5583999601813</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Wg</t>
+          <t>Mayara</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Wg Refrigeracao</t>
+          <t>Mayara Leal Firmino da Silva</t>
         </is>
       </c>
     </row>
     <row r="44" ht="15.75" customHeight="1" s="3">
       <c r="A44" s="4" t="n">
-        <v>5583981179397</v>
+        <v>5583986153195</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Airton</t>
+          <t>Artur</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Airton Barbosa de Araujo Liberato</t>
+          <t>Artur Guilherme da Silva Rufo</t>
         </is>
       </c>
     </row>
     <row r="45" ht="15.75" customHeight="1" s="3">
       <c r="A45" s="4" t="n">
-        <v>5583991665028</v>
+        <v>5583999217986</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Emmanuelle</t>
+          <t>Edificio</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Emmanuelle Pereira</t>
+          <t>Edificio Atlantico Sul Residence</t>
         </is>
       </c>
     </row>
     <row r="46" ht="15.75" customHeight="1" s="3">
       <c r="A46" s="4" t="n">
-        <v>5583988911246</v>
+        <v>5583999818805</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Lucio</t>
+          <t>Yazbek</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Lucio Carvalho Machado</t>
+          <t>Yazbek Lighting</t>
         </is>
       </c>
     </row>
     <row r="47" ht="15.75" customHeight="1" s="3">
       <c r="A47" s="4" t="n">
-        <v>5583987849457</v>
+        <v>5583996615352</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Ana</t>
+          <t>Carolina</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Ana Cristina Lima Bezerra</t>
+          <t>Carolina Alves Bernardo</t>
         </is>
       </c>
     </row>
     <row r="48" ht="15.75" customHeight="1" s="3">
       <c r="A48" s="4" t="n">
-        <v>5583987687054</v>
+        <v>5583988785668</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Clemilde</t>
+          <t>Jose</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Clemilde dos Santos Falcao</t>
+          <t>Jose Herculano de Aquino</t>
         </is>
       </c>
     </row>
     <row r="49" ht="15.75" customHeight="1" s="3">
       <c r="A49" s="4" t="n">
-        <v>5583991306557</v>
+        <v>5583987160191</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Jonhdiego</t>
+          <t>Alexsandro</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Jonhdiego dos Santos Silva</t>
+          <t>Alexsandro Gomes</t>
         </is>
       </c>
     </row>
     <row r="50" ht="15.75" customHeight="1" s="3">
       <c r="A50" s="4" t="n">
-        <v>5583993421999</v>
+        <v>5583988988435</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Emmyle</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Maria de Lourdes dos Santos Miranda</t>
+          <t>Emmyle Sobral</t>
         </is>
       </c>
     </row>
     <row r="51" ht="15.75" customHeight="1" s="3">
       <c r="A51" s="4" t="n">
-        <v>5583996068960</v>
+        <v>5583999818919</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Agnes</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Maria de Fatima Maia Pessoa</t>
+          <t>Agnes Pauli Pontes de Aquino</t>
         </is>
       </c>
     </row>
